--- a/output/Part_Summary_Wistron_VV726800136.xlsx
+++ b/output/Part_Summary_Wistron_VV726800136.xlsx
@@ -798,14 +798,17 @@
       </c>
       <c r="I12" s="9">
         <f>G12*H12</f>
+        <v>120122.4</v>
         <v/>
       </c>
       <c r="J12" s="10">
         <f>G12*INDEX('Packing list'!$C$4:$C$8,MATCH(F12,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F12,'Packing list'!$A$4:$A$8,0))</f>
+        <v>142.32</v>
         <v/>
       </c>
       <c r="K12" s="10">
         <f>G12*INDEX('Packing list'!$D$4:$D$8,MATCH(F12,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F12,'Packing list'!$A$4:$A$8,0))</f>
+        <v>225</v>
         <v/>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -853,14 +856,17 @@
       </c>
       <c r="I13" s="9">
         <f>G13*H13</f>
+        <v>74722.56</v>
         <v/>
       </c>
       <c r="J13" s="10">
         <f>G13*INDEX('Packing list'!$C$4:$C$8,MATCH(F13,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F13,'Packing list'!$A$4:$A$8,0))</f>
+        <v>96</v>
         <v/>
       </c>
       <c r="K13" s="10">
         <f>G13*INDEX('Packing list'!$D$4:$D$8,MATCH(F13,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F13,'Packing list'!$A$4:$A$8,0))</f>
+        <v>166</v>
         <v/>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -908,14 +914,17 @@
       </c>
       <c r="I14" s="9">
         <f>G14*H14</f>
+        <v>5310.76</v>
         <v/>
       </c>
       <c r="J14" s="10">
         <f>G14*INDEX('Packing list'!$C$4:$C$8,MATCH(F14,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F14,'Packing list'!$A$4:$A$8,0))</f>
+        <v>6.6076705882</v>
         <v/>
       </c>
       <c r="K14" s="10">
         <f>G14*INDEX('Packing list'!$D$4:$D$8,MATCH(F14,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F14,'Packing list'!$A$4:$A$8,0))</f>
+        <v>19.4044117647</v>
         <v/>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -963,14 +972,17 @@
       </c>
       <c r="I15" s="9">
         <f>G15*H15</f>
+        <v>15807.96</v>
         <v/>
       </c>
       <c r="J15" s="10">
         <f>G15*INDEX('Packing list'!$C$4:$C$8,MATCH(F15,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F15,'Packing list'!$A$4:$A$8,0))</f>
+        <v>13.7236235294</v>
         <v/>
       </c>
       <c r="K15" s="10">
         <f>G15*INDEX('Packing list'!$D$4:$D$8,MATCH(F15,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F15,'Packing list'!$A$4:$A$8,0))</f>
+        <v>40.3014705882</v>
         <v/>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1018,14 +1030,17 @@
       </c>
       <c r="I16" s="9">
         <f>G16*H16</f>
+        <v>42518.4</v>
         <v/>
       </c>
       <c r="J16" s="10">
         <f>G16*INDEX('Packing list'!$C$4:$C$8,MATCH(F16,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F16,'Packing list'!$A$4:$A$8,0))</f>
+        <v>4.3567058824</v>
         <v/>
       </c>
       <c r="K16" s="10">
         <f>G16*INDEX('Packing list'!$D$4:$D$8,MATCH(F16,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F16,'Packing list'!$A$4:$A$8,0))</f>
+        <v>12.7941176471</v>
         <v/>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1073,14 +1088,17 @@
       </c>
       <c r="I17" s="9">
         <f>G17*H17</f>
+        <v>5230.8</v>
         <v/>
       </c>
       <c r="J17" s="10">
         <f>G17*INDEX('Packing list'!$C$4:$C$8,MATCH(F17,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F17,'Packing list'!$A$4:$A$8,0))</f>
+        <v>9</v>
         <v/>
       </c>
       <c r="K17" s="10">
         <f>G17*INDEX('Packing list'!$D$4:$D$8,MATCH(F17,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F17,'Packing list'!$A$4:$A$8,0))</f>
+        <v>33</v>
         <v/>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1128,14 +1146,17 @@
       </c>
       <c r="I18" s="9">
         <f>G18*H18</f>
+        <v>24665.76</v>
         <v/>
       </c>
       <c r="J18" s="10">
         <f>G18*INDEX('Packing list'!$C$4:$C$8,MATCH(F18,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F18,'Packing list'!$A$4:$A$8,0))</f>
+        <v>50.4</v>
         <v/>
       </c>
       <c r="K18" s="10">
         <f>G18*INDEX('Packing list'!$D$4:$D$8,MATCH(F18,'Packing list'!$A$4:$A$8,0))/INDEX('Packing list'!$B$4:$B$8,MATCH(F18,'Packing list'!$A$4:$A$8,0))</f>
+        <v>100</v>
         <v/>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1161,19 +1182,23 @@
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="13">
         <f>SUM(G12:G18)</f>
+        <v>2500</v>
         <v/>
       </c>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="14">
         <f>SUM(I12:I18)</f>
+        <v>288378.64</v>
         <v/>
       </c>
       <c r="J19" s="15">
         <f>SUM(J12:J18)</f>
+        <v>322.408</v>
         <v/>
       </c>
       <c r="K19" s="15">
         <f>SUM(K12:K18)</f>
+        <v>596.5</v>
         <v/>
       </c>
       <c r="L19" s="12" t="n"/>
@@ -1186,6 +1211,7 @@
       </c>
       <c r="G21" s="17">
         <f>I19</f>
+        <v>288378.64</v>
         <v/>
       </c>
     </row>
@@ -1448,18 +1474,22 @@
       </c>
       <c r="B9" s="13">
         <f>SUM(B4:B8)</f>
+        <v>2500</v>
         <v/>
       </c>
       <c r="C9" s="15">
         <f>SUM(C4:C8)</f>
+        <v>322.408</v>
         <v/>
       </c>
       <c r="D9" s="15">
         <f>SUM(D4:D8)</f>
+        <v>596.5</v>
         <v/>
       </c>
       <c r="E9" s="12">
         <f>SUM(E4:E8)</f>
+        <v>76</v>
         <v/>
       </c>
       <c r="F9" s="12" t="n"/>
